--- a/FACS_summary.xlsx
+++ b/FACS_summary.xlsx
@@ -1,44 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://technionmail-my.sharepoint.com/personal/kra_valeriia_campus_technion_ac_il/Documents/Desktop/LAB/WRITING/papers/biosensor_paper/analysis/scripts/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://technionmail-my.sharepoint.com/personal/kra_valeriia_campus_technion_ac_il/Documents/Desktop/LAB/WRITING/papers/BIOSENSORS PAPER/REVISION_iScience/SUBMISSION_iScience/04_data_and_code_for_github/codes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="105" documentId="8_{B487A4E9-83F7-40F5-AC65-12DF016C6DA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CA56D31-A222-4ECC-93F1-14716F651EB9}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_76C30A0F19FD029757DA9F6F0721C3A5D6A2EFCA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5980E2D-C4F1-44B3-8126-96906D69C810}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6C668A4D-850D-44B7-B81F-F3B0A0099F9E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Butyrate" sheetId="1" r:id="rId1"/>
     <sheet name="Heme" sheetId="2" r:id="rId2"/>
     <sheet name="Lactate" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="16">
+  <si>
+    <t>time [Hours]</t>
+  </si>
   <si>
     <t>Butyrate concentration [mM]</t>
   </si>
@@ -55,9 +42,6 @@
     <t>BD4</t>
   </si>
   <si>
-    <t>time [Hours]</t>
-  </si>
-  <si>
     <t>Heme concentration [uM]</t>
   </si>
   <si>
@@ -68,6 +52,9 @@
   </si>
   <si>
     <t>HD3</t>
+  </si>
+  <si>
+    <t>HD4</t>
   </si>
   <si>
     <t>Lactate concentration [mM]</t>
@@ -84,25 +71,16 @@
   <si>
     <t>LD4</t>
   </si>
-  <si>
-    <t>HD4</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -134,7 +112,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -157,44 +135,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -221,32 +199,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -273,24 +233,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -302,224 +244,228 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED0F636F-76C5-4922-AA94-A3B1A06D68D8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" t="s">
+        <v>4</v>
+      </c>
+      <c r="M1" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1" t="s">
+        <v>4</v>
+      </c>
+      <c r="O1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O1" t="s">
-        <v>4</v>
-      </c>
       <c r="P1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -583,7 +529,6 @@
         <v>21</v>
       </c>
       <c r="B3">
-        <f>B2/2</f>
         <v>50</v>
       </c>
       <c r="C3">
@@ -640,7 +585,6 @@
         <v>21</v>
       </c>
       <c r="B4">
-        <f t="shared" ref="B4:B12" si="0">B3/2</f>
         <v>25</v>
       </c>
       <c r="C4">
@@ -697,7 +641,6 @@
         <v>21</v>
       </c>
       <c r="B5">
-        <f t="shared" si="0"/>
         <v>12.5</v>
       </c>
       <c r="C5">
@@ -754,7 +697,6 @@
         <v>21</v>
       </c>
       <c r="B6">
-        <f t="shared" si="0"/>
         <v>6.25</v>
       </c>
       <c r="C6">
@@ -811,7 +753,6 @@
         <v>21</v>
       </c>
       <c r="B7">
-        <f t="shared" si="0"/>
         <v>3.125</v>
       </c>
       <c r="C7">
@@ -868,7 +809,6 @@
         <v>21</v>
       </c>
       <c r="B8">
-        <f t="shared" si="0"/>
         <v>1.5625</v>
       </c>
       <c r="C8">
@@ -925,7 +865,6 @@
         <v>21</v>
       </c>
       <c r="B9">
-        <f t="shared" si="0"/>
         <v>0.78125</v>
       </c>
       <c r="C9">
@@ -982,7 +921,6 @@
         <v>21</v>
       </c>
       <c r="B10">
-        <f t="shared" si="0"/>
         <v>0.390625</v>
       </c>
       <c r="C10">
@@ -1039,7 +977,6 @@
         <v>21</v>
       </c>
       <c r="B11">
-        <f t="shared" si="0"/>
         <v>0.1953125</v>
       </c>
       <c r="C11">
@@ -1096,7 +1033,6 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <f t="shared" si="0"/>
         <v>9.765625E-2</v>
       </c>
       <c r="C12">
@@ -1205,19 +1141,18 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29B3F763-0CC9-4DC1-8620-14EA4646B16A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>6</v>
@@ -1250,13 +1185,13 @@
         <v>9</v>
       </c>
       <c r="L1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="N1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -1264,7 +1199,6 @@
         <v>21</v>
       </c>
       <c r="B2">
-        <f>12.5</f>
         <v>12.5</v>
       </c>
       <c r="C2">
@@ -1309,7 +1243,6 @@
         <v>21</v>
       </c>
       <c r="B3">
-        <f t="shared" ref="B3:B11" si="0">B2/2</f>
         <v>6.25</v>
       </c>
       <c r="C3">
@@ -1354,7 +1287,6 @@
         <v>21</v>
       </c>
       <c r="B4">
-        <f t="shared" si="0"/>
         <v>3.125</v>
       </c>
       <c r="C4">
@@ -1399,7 +1331,6 @@
         <v>21</v>
       </c>
       <c r="B5">
-        <f t="shared" si="0"/>
         <v>1.5625</v>
       </c>
       <c r="C5">
@@ -1444,7 +1375,6 @@
         <v>21</v>
       </c>
       <c r="B6">
-        <f t="shared" si="0"/>
         <v>0.78125</v>
       </c>
       <c r="C6">
@@ -1489,7 +1419,6 @@
         <v>21</v>
       </c>
       <c r="B7">
-        <f t="shared" si="0"/>
         <v>0.390625</v>
       </c>
       <c r="C7">
@@ -1534,7 +1463,6 @@
         <v>21</v>
       </c>
       <c r="B8">
-        <f t="shared" si="0"/>
         <v>0.1953125</v>
       </c>
       <c r="F8">
@@ -1570,7 +1498,6 @@
         <v>21</v>
       </c>
       <c r="B9">
-        <f t="shared" si="0"/>
         <v>9.765625E-2</v>
       </c>
       <c r="F9">
@@ -1606,7 +1533,6 @@
         <v>21</v>
       </c>
       <c r="B10">
-        <f t="shared" si="0"/>
         <v>4.8828125E-2</v>
       </c>
       <c r="F10">
@@ -1642,7 +1568,6 @@
         <v>21</v>
       </c>
       <c r="B11">
-        <f t="shared" si="0"/>
         <v>2.44140625E-2</v>
       </c>
       <c r="F11">
@@ -1718,63 +1643,66 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37FD662C-4C09-43DB-94CD-8B2CBB85A20D}">
-  <dimension ref="A1:O13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:P13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M1" t="s">
         <v>14</v>
       </c>
       <c r="N1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>21</v>
       </c>
@@ -1790,13 +1718,36 @@
       <c r="E2">
         <v>1058684.3</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F2">
+        <v>25515.0498046875</v>
+      </c>
+      <c r="G2">
+        <v>29542.5</v>
+      </c>
+      <c r="H2">
+        <v>35678.25</v>
+      </c>
+      <c r="I2">
+        <v>29749.400390625</v>
+      </c>
+      <c r="J2">
+        <v>108393.44921875</v>
+      </c>
+      <c r="K2">
+        <v>126565.3984375</v>
+      </c>
+      <c r="L2">
+        <v>28715.599609375</v>
+      </c>
+      <c r="M2">
+        <v>142568.09375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>21</v>
       </c>
       <c r="B3">
-        <f>B2/2</f>
         <v>100</v>
       </c>
       <c r="C3">
@@ -1809,42 +1760,44 @@
         <v>1061803.8999999999</v>
       </c>
       <c r="F3">
-        <v>121272</v>
+        <v>22613.2001953125</v>
       </c>
       <c r="G3">
-        <v>164066.5</v>
+        <v>23410.900390625</v>
       </c>
       <c r="H3">
-        <v>215995.8</v>
+        <v>22678.400390625</v>
       </c>
       <c r="I3">
-        <v>162501.4</v>
+        <v>13287.099609375</v>
       </c>
       <c r="J3">
-        <v>132041.79999999999</v>
+        <v>124275.1484375</v>
       </c>
       <c r="K3">
-        <v>210351.3</v>
+        <v>103364.046875</v>
       </c>
       <c r="L3">
-        <v>142410.4</v>
+        <v>68310.296875</v>
       </c>
       <c r="M3">
+        <v>143680.953125</v>
+      </c>
+      <c r="N3">
         <v>585932.1</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>946286.8</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>579654.1</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>21</v>
       </c>
       <c r="B4">
-        <f t="shared" ref="B4:B12" si="0">B3/2</f>
         <v>50</v>
       </c>
       <c r="C4">
@@ -1857,42 +1810,44 @@
         <v>893242.9</v>
       </c>
       <c r="F4">
-        <v>149872</v>
+        <v>16506.400390625</v>
       </c>
       <c r="G4">
-        <v>142220.5</v>
+        <v>18911.5</v>
       </c>
       <c r="H4">
-        <v>159653.5</v>
+        <v>14059.2998046875</v>
       </c>
       <c r="I4">
-        <v>122891.3</v>
+        <v>6295</v>
       </c>
       <c r="J4">
-        <v>123797.3</v>
+        <v>127615.40234375</v>
       </c>
       <c r="K4">
-        <v>173870</v>
+        <v>94716</v>
       </c>
       <c r="L4">
-        <v>139373.9</v>
+        <v>32415.900390625</v>
       </c>
       <c r="M4">
+        <v>147644.1484375</v>
+      </c>
+      <c r="N4">
         <v>603701.9</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>859834.1</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>612514.80000000005</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>21</v>
       </c>
       <c r="B5">
-        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="C5">
@@ -1905,42 +1860,44 @@
         <v>627523.69999999995</v>
       </c>
       <c r="F5">
-        <v>164662.20000000001</v>
+        <v>11094.0498046875</v>
       </c>
       <c r="G5">
-        <v>126828.5</v>
+        <v>9877.5</v>
       </c>
       <c r="H5">
-        <v>126478.6</v>
+        <v>12615.89990234375</v>
       </c>
       <c r="I5">
-        <v>93819.5</v>
+        <v>4353.7998046875</v>
       </c>
       <c r="J5">
-        <v>187497.1</v>
+        <v>125755.1015625</v>
       </c>
       <c r="K5">
-        <v>260077.5</v>
+        <v>119238.1015625</v>
       </c>
       <c r="L5">
-        <v>209220.1</v>
+        <v>160301.046875</v>
       </c>
       <c r="M5">
+        <v>170975.09375</v>
+      </c>
+      <c r="N5">
         <v>498259.4</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>780381.8</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>498516</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>21</v>
       </c>
       <c r="B6">
-        <f t="shared" si="0"/>
         <v>12.5</v>
       </c>
       <c r="C6">
@@ -1953,42 +1910,44 @@
         <v>458155.9</v>
       </c>
       <c r="F6">
-        <v>256649.5</v>
+        <v>16719</v>
       </c>
       <c r="G6">
-        <v>252989.4</v>
+        <v>4035.199951171875</v>
       </c>
       <c r="H6">
-        <v>184452.5</v>
+        <v>20051.2001953125</v>
       </c>
       <c r="I6">
-        <v>132885</v>
+        <v>9766.75</v>
       </c>
       <c r="J6">
-        <v>311024.5</v>
+        <v>183574.3984375</v>
       </c>
       <c r="K6">
-        <v>407049.9</v>
+        <v>194771.8515625</v>
       </c>
       <c r="L6">
-        <v>272400.7</v>
+        <v>203744</v>
       </c>
       <c r="M6">
+        <v>232734.75</v>
+      </c>
+      <c r="N6">
         <v>387578.7</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>441043.1</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>438382.7</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>21</v>
       </c>
       <c r="B7">
-        <f t="shared" si="0"/>
         <v>6.25</v>
       </c>
       <c r="C7">
@@ -2001,42 +1960,44 @@
         <v>331030.8</v>
       </c>
       <c r="F7">
-        <v>490313.8</v>
+        <v>39618.80078125</v>
       </c>
       <c r="G7">
-        <v>464444.2</v>
+        <v>11045</v>
       </c>
       <c r="H7">
-        <v>381958.3</v>
+        <v>41114.5</v>
       </c>
       <c r="I7">
-        <v>292319.40000000002</v>
+        <v>34431.6015625</v>
       </c>
       <c r="J7">
-        <v>402363.1</v>
+        <v>280795.40625</v>
       </c>
       <c r="K7">
-        <v>518035.8</v>
+        <v>237616.34375</v>
       </c>
       <c r="L7">
-        <v>353810.1</v>
+        <v>389916.8125</v>
       </c>
       <c r="M7">
+        <v>282391.8125</v>
+      </c>
+      <c r="N7">
         <v>393828.4</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>568694.5</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>397877.9</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>21</v>
       </c>
       <c r="B8">
-        <f t="shared" si="0"/>
         <v>3.125</v>
       </c>
       <c r="C8">
@@ -2049,42 +2010,44 @@
         <v>264398.5</v>
       </c>
       <c r="F8">
-        <v>797803</v>
+        <v>163661.703125</v>
       </c>
       <c r="G8">
-        <v>709759</v>
+        <v>45528.599609375</v>
       </c>
       <c r="H8">
-        <v>761284.2</v>
+        <v>237281</v>
       </c>
       <c r="I8">
-        <v>499472.7</v>
+        <v>253674.796875</v>
       </c>
       <c r="J8">
-        <v>496426.4</v>
+        <v>357039.3125</v>
       </c>
       <c r="K8">
-        <v>588787.9</v>
+        <v>327961.203125</v>
       </c>
       <c r="L8">
-        <v>425722.2</v>
+        <v>494644.953125</v>
       </c>
       <c r="M8">
+        <v>355272.140625</v>
+      </c>
+      <c r="N8">
         <v>368119.8</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>446002.3</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>364035.2</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>21</v>
       </c>
       <c r="B9">
-        <f t="shared" si="0"/>
         <v>1.5625</v>
       </c>
       <c r="C9">
@@ -2097,42 +2060,44 @@
         <v>210666.8</v>
       </c>
       <c r="F9">
-        <v>1060721.6000000001</v>
+        <v>773087.9375</v>
       </c>
       <c r="G9">
-        <v>1032918</v>
+        <v>334760.59375</v>
       </c>
       <c r="H9">
-        <v>1094314</v>
+        <v>636420.8125</v>
       </c>
       <c r="I9">
-        <v>721269.7</v>
+        <v>608346.34375</v>
       </c>
       <c r="J9">
-        <v>597494.30000000005</v>
+        <v>400525.90625</v>
       </c>
       <c r="K9">
-        <v>691626.7</v>
+        <v>361669.8125</v>
       </c>
       <c r="L9">
-        <v>659294</v>
+        <v>647792.6875</v>
       </c>
       <c r="M9">
+        <v>372750.5</v>
+      </c>
+      <c r="N9">
         <v>323142.7</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>284402.40000000002</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>293722.40000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>21</v>
       </c>
       <c r="B10">
-        <f t="shared" si="0"/>
         <v>0.78125</v>
       </c>
       <c r="C10">
@@ -2145,42 +2110,44 @@
         <v>178154</v>
       </c>
       <c r="F10">
-        <v>1411652</v>
+        <v>1126215.75</v>
       </c>
       <c r="G10">
-        <v>1300155.8</v>
+        <v>716477.625</v>
       </c>
       <c r="H10">
-        <v>1176078</v>
+        <v>867650.875</v>
       </c>
       <c r="I10">
-        <v>1103539.5</v>
+        <v>957644.75</v>
       </c>
       <c r="J10">
-        <v>755078.6</v>
+        <v>456943.90625</v>
       </c>
       <c r="K10">
-        <v>776296.2</v>
+        <v>390109.90625</v>
       </c>
       <c r="L10">
-        <v>645015.9</v>
+        <v>736635.125</v>
       </c>
       <c r="M10">
+        <v>402992.09375</v>
+      </c>
+      <c r="N10">
         <v>290187.09999999998</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>220421.3</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>262910.09999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>21</v>
       </c>
       <c r="B11">
-        <f t="shared" si="0"/>
         <v>0.390625</v>
       </c>
       <c r="C11">
@@ -2193,42 +2160,44 @@
         <v>157527.20000000001</v>
       </c>
       <c r="F11">
-        <v>1545355.9</v>
+        <v>1261511.1875</v>
       </c>
       <c r="G11">
-        <v>1568621.1</v>
+        <v>1004640.875</v>
       </c>
       <c r="H11">
-        <v>1345984.5</v>
+        <v>1036073.5</v>
       </c>
       <c r="I11">
-        <v>1403678.6</v>
+        <v>889356.1875</v>
       </c>
       <c r="J11">
-        <v>824559.6</v>
+        <v>462873.546875</v>
       </c>
       <c r="K11">
-        <v>887848.1</v>
+        <v>419822.40625</v>
       </c>
       <c r="L11">
-        <v>861448.9</v>
+        <v>762341.3125</v>
       </c>
       <c r="M11">
+        <v>429100.90625</v>
+      </c>
+      <c r="N11">
         <v>277463.59999999998</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>208350.7</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>238141.2</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>21</v>
       </c>
       <c r="B12">
-        <f t="shared" si="0"/>
         <v>0.1953125</v>
       </c>
       <c r="C12">
@@ -2241,37 +2210,40 @@
         <v>133385.29999999999</v>
       </c>
       <c r="F12">
-        <v>1590313.8</v>
+        <v>1364349.5</v>
       </c>
       <c r="G12">
-        <v>2055341.8</v>
+        <v>1103385.25</v>
       </c>
       <c r="H12">
-        <v>1462859.5</v>
+        <v>1022365.84375</v>
       </c>
       <c r="I12">
-        <v>1549228.8</v>
+        <v>1211122.75</v>
       </c>
       <c r="J12">
-        <v>961427.6</v>
+        <v>474573.0625</v>
       </c>
       <c r="K12">
-        <v>888740</v>
+        <v>418721.90625</v>
       </c>
       <c r="L12">
-        <v>1200750.1000000001</v>
+        <v>748132.3125</v>
       </c>
       <c r="M12">
+        <v>444978.09375</v>
+      </c>
+      <c r="N12">
         <v>257997.1</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>227078.8</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>210918</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>21</v>
       </c>
@@ -2288,37 +2260,40 @@
         <v>98429</v>
       </c>
       <c r="F13">
-        <v>1682507.3</v>
+        <v>1427685.5</v>
       </c>
       <c r="G13">
-        <v>2019815.3</v>
+        <v>1352088.8125</v>
       </c>
       <c r="H13">
-        <v>1434567.9</v>
+        <v>1403380.375</v>
       </c>
       <c r="I13">
-        <v>1709521.1</v>
+        <v>1418972.0625</v>
       </c>
       <c r="J13">
-        <v>1285985.3</v>
+        <v>511069.90625</v>
       </c>
       <c r="K13">
-        <v>962373</v>
+        <v>474423.09375</v>
       </c>
       <c r="L13">
-        <v>1032475.6</v>
+        <v>767689.1875</v>
       </c>
       <c r="M13">
+        <v>504291.40625</v>
+      </c>
+      <c r="N13">
         <v>231061.5</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>256402.3</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>193681.8</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>